--- a/data/albums.xlsx
+++ b/data/albums.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/freekver/Documents/personal/albums/albums/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B8CFA20-9B38-E744-9C63-8B6DE119415B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0262AA33-DABF-0D4E-8C1F-502F9620FE09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7700" yWindow="1580" windowWidth="40520" windowHeight="23820" xr2:uid="{1D22D18E-AD96-8846-9551-E8ACDE6B1955}"/>
+    <workbookView xWindow="38400" yWindow="2720" windowWidth="30240" windowHeight="18880" xr2:uid="{1D22D18E-AD96-8846-9551-E8ACDE6B1955}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2183" uniqueCount="1389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2199" uniqueCount="1398">
   <si>
     <t>King Of The Delta Blues Singers</t>
   </si>
@@ -2775,9 +2775,6 @@
     <t>Duke Ellington</t>
   </si>
   <si>
-    <t>Anthology</t>
-  </si>
-  <si>
     <t>Howlin' Wolf</t>
   </si>
   <si>
@@ -3852,9 +3849,6 @@
     <t>JJ Grey</t>
   </si>
   <si>
-    <t>Cannot Be Satisfied: The Very Best Of Muddy Waters</t>
-  </si>
-  <si>
     <t>j</t>
   </si>
   <si>
@@ -4222,6 +4216,39 @@
   </si>
   <si>
     <t>Faithless</t>
+  </si>
+  <si>
+    <t>Moanin' in the midnight</t>
+  </si>
+  <si>
+    <t>Hard Again</t>
+  </si>
+  <si>
+    <t>John Lee Hooker</t>
+  </si>
+  <si>
+    <t>The Real Folk Blues</t>
+  </si>
+  <si>
+    <t>Blues Breakers</t>
+  </si>
+  <si>
+    <t>John Mayall &amp; the Blues Breakers</t>
+  </si>
+  <si>
+    <t>Boomer’s Story</t>
+  </si>
+  <si>
+    <t>The Progressive Blues Experiment</t>
+  </si>
+  <si>
+    <t>Johnny Winter</t>
+  </si>
+  <si>
+    <t>Texas Flood</t>
+  </si>
+  <si>
+    <t>Stephie Ray Vaughn</t>
   </si>
 </sst>
 </file>
@@ -4247,7 +4274,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4257,6 +4284,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4274,10 +4307,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -4597,7 +4632,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4340B13D-1155-C848-B06E-C8AEF830FD9E}">
-  <dimension ref="A1:E923"/>
+  <dimension ref="A1:E928"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="1" customWidth="1"/>
@@ -4610,7 +4645,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="B1">
         <v>1937</v>
@@ -4624,7 +4659,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="B2">
         <v>1957</v>
@@ -4638,7 +4673,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B3">
         <v>1957</v>
@@ -4652,13 +4687,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="B4">
         <v>1958</v>
       </c>
       <c r="C4" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="D4" t="s">
         <v>29</v>
@@ -4666,7 +4701,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="B5">
         <v>1959</v>
@@ -4680,7 +4715,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="B6">
         <v>1959</v>
@@ -4694,7 +4729,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B7">
         <v>1959</v>
@@ -4708,7 +4743,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="B8">
         <v>1960</v>
@@ -4722,7 +4757,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B9">
         <v>1960</v>
@@ -4736,7 +4771,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B10">
         <v>1961</v>
@@ -4750,7 +4785,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="B11">
         <v>1963</v>
@@ -4788,7 +4823,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B14">
         <v>1964</v>
@@ -4814,7 +4849,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="B16">
         <v>1964</v>
@@ -4828,7 +4863,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="B17">
         <v>1964</v>
@@ -4857,7 +4892,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="B19">
         <v>1965</v>
@@ -4895,7 +4930,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B22">
         <v>1965</v>
@@ -4945,13 +4980,13 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B26">
         <v>1966</v>
       </c>
       <c r="C26" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="D26" t="s">
         <v>19</v>
@@ -4995,7 +5030,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B30">
         <v>1966</v>
@@ -5009,7 +5044,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B31">
         <v>1966</v>
@@ -5023,7 +5058,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B32">
         <v>1967</v>
@@ -5037,7 +5072,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B33">
         <v>1967</v>
@@ -5138,7 +5173,7 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="B41">
         <v>1968</v>
@@ -5152,7 +5187,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="B42">
         <v>1968</v>
@@ -5166,7 +5201,7 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="B43">
         <v>1968</v>
@@ -5180,7 +5215,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>1311</v>
+        <v>1266</v>
       </c>
       <c r="B44">
         <v>1968</v>
@@ -5209,7 +5244,7 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="B46">
         <v>1968</v>
@@ -5271,7 +5306,7 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B51">
         <v>1968</v>
@@ -5285,7 +5320,7 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="B52">
         <v>1969</v>
@@ -5311,7 +5346,7 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B54">
         <v>1969</v>
@@ -5385,7 +5420,7 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B60">
         <v>1969</v>
@@ -5411,7 +5446,7 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="B62">
         <v>1969</v>
@@ -5425,7 +5460,7 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="B63">
         <v>1969</v>
@@ -5451,13 +5486,13 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="B65">
         <v>1969</v>
       </c>
       <c r="C65" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="D65" t="s">
         <v>100</v>
@@ -5465,7 +5500,7 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B66">
         <v>1969</v>
@@ -5527,7 +5562,7 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="B71">
         <v>1970</v>
@@ -5541,13 +5576,13 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B72">
         <v>1970</v>
       </c>
       <c r="C72" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="D72" t="s">
         <v>108</v>
@@ -5555,7 +5590,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="B73">
         <v>1970</v>
@@ -5581,7 +5616,7 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B75">
         <v>1970</v>
@@ -5667,7 +5702,7 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B82">
         <v>1970</v>
@@ -5681,7 +5716,7 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="B83">
         <v>1970</v>
@@ -5695,7 +5730,7 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B84">
         <v>1971</v>
@@ -5709,7 +5744,7 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B85">
         <v>1971</v>
@@ -5735,7 +5770,7 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="B87">
         <v>1971</v>
@@ -5749,7 +5784,7 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B88">
         <v>1971</v>
@@ -5775,7 +5810,7 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B90">
         <v>1971</v>
@@ -5801,7 +5836,7 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="B92">
         <v>1971</v>
@@ -5815,7 +5850,7 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B93">
         <v>1971</v>
@@ -5829,13 +5864,13 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B94">
         <v>1971</v>
       </c>
       <c r="C94" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="D94" t="s">
         <v>137</v>
@@ -5843,7 +5878,7 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B95">
         <v>1972</v>
@@ -5864,12 +5899,12 @@
         <v>139</v>
       </c>
       <c r="D96" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B97">
         <v>1972</v>
@@ -5883,13 +5918,13 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="B98">
         <v>1972</v>
       </c>
       <c r="C98" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="D98" t="s">
         <v>87</v>
@@ -5909,7 +5944,7 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B100">
         <v>1972</v>
@@ -5923,7 +5958,7 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B101">
         <v>1972</v>
@@ -5937,7 +5972,7 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="B102">
         <v>1972</v>
@@ -5951,7 +5986,7 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="B103">
         <v>1972</v>
@@ -5965,7 +6000,7 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="B104">
         <v>1972</v>
@@ -6015,7 +6050,7 @@
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B108">
         <v>1972</v>
@@ -6089,7 +6124,7 @@
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="B114">
         <v>1973</v>
@@ -6131,7 +6166,7 @@
         <v>1973</v>
       </c>
       <c r="C117" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="D117" t="s">
         <v>58</v>
@@ -6139,13 +6174,13 @@
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B118">
         <v>1974</v>
       </c>
       <c r="C118" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="D118" t="s">
         <v>64</v>
@@ -6213,7 +6248,7 @@
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B124">
         <v>1974</v>
@@ -6251,7 +6286,7 @@
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="B127">
         <v>1975</v>
@@ -6313,7 +6348,7 @@
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B132">
         <v>1975</v>
@@ -6327,13 +6362,13 @@
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="B133">
         <v>1975</v>
       </c>
       <c r="C133" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="D133" t="s">
         <v>187</v>
@@ -6369,7 +6404,7 @@
         <v>1975</v>
       </c>
       <c r="C136" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D136" t="s">
         <v>126</v>
@@ -6425,7 +6460,7 @@
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B141">
         <v>1976</v>
@@ -6439,7 +6474,7 @@
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="B142">
         <v>1976</v>
@@ -6453,7 +6488,7 @@
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B143">
         <v>1976</v>
@@ -6467,7 +6502,7 @@
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="B144">
         <v>1976</v>
@@ -6493,7 +6528,7 @@
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="B146">
         <v>1977</v>
@@ -6507,7 +6542,7 @@
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B147">
         <v>1977</v>
@@ -6521,7 +6556,7 @@
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="B148">
         <v>1977</v>
@@ -6583,7 +6618,7 @@
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="B153">
         <v>1978</v>
@@ -6625,7 +6660,7 @@
         <v>1978</v>
       </c>
       <c r="C156" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="D156" t="s">
         <v>126</v>
@@ -6637,7 +6672,7 @@
         <v>1979</v>
       </c>
       <c r="C157" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="D157" t="s">
         <v>211</v>
@@ -6693,7 +6728,7 @@
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="B162">
         <v>1979</v>
@@ -6899,7 +6934,7 @@
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B179">
         <v>1981</v>
@@ -6949,7 +6984,7 @@
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="B183">
         <v>1982</v>
@@ -7026,7 +7061,7 @@
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="B189">
         <v>1983</v>
@@ -7100,7 +7135,7 @@
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B195">
         <v>1983</v>
@@ -7126,7 +7161,7 @@
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B197">
         <v>1984</v>
@@ -7164,7 +7199,7 @@
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B200">
         <v>1984</v>
@@ -7202,7 +7237,7 @@
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B203">
         <v>1984</v>
@@ -7276,7 +7311,7 @@
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="B209">
         <v>1985</v>
@@ -7302,7 +7337,7 @@
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="B211">
         <v>1986</v>
@@ -7328,7 +7363,7 @@
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="B213">
         <v>1986</v>
@@ -7378,7 +7413,7 @@
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="B217">
         <v>1987</v>
@@ -7440,7 +7475,7 @@
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B222">
         <v>1987</v>
@@ -7466,7 +7501,7 @@
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="B224">
         <v>1987</v>
@@ -7508,7 +7543,7 @@
         <v>1988</v>
       </c>
       <c r="C227" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="D227" t="s">
         <v>307</v>
@@ -7588,7 +7623,7 @@
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="B234">
         <v>1989</v>
@@ -7633,7 +7668,7 @@
         <v>321</v>
       </c>
       <c r="D237" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.2">
@@ -7674,7 +7709,7 @@
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="B241">
         <v>1990</v>
@@ -7712,7 +7747,7 @@
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="B244">
         <v>1991</v>
@@ -7774,7 +7809,7 @@
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="B249">
         <v>1991</v>
@@ -7812,7 +7847,7 @@
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="B252">
         <v>1991</v>
@@ -7826,7 +7861,7 @@
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
       <c r="B253">
         <v>1991</v>
@@ -7864,7 +7899,7 @@
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B256">
         <v>1992</v>
@@ -7878,7 +7913,7 @@
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B257">
         <v>1992</v>
@@ -7904,7 +7939,7 @@
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="B259">
         <v>1992</v>
@@ -7930,7 +7965,7 @@
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B261">
         <v>1992</v>
@@ -7992,7 +8027,7 @@
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="B266">
         <v>1993</v>
@@ -8054,7 +8089,7 @@
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="B271">
         <v>1993</v>
@@ -8080,7 +8115,7 @@
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="B273">
         <v>1993</v>
@@ -8106,7 +8141,7 @@
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="B275">
         <v>1994</v>
@@ -8144,7 +8179,7 @@
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="B278">
         <v>1994</v>
@@ -8158,7 +8193,7 @@
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="B279">
         <v>1994</v>
@@ -8208,7 +8243,7 @@
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B283">
         <v>1994</v>
@@ -8222,7 +8257,7 @@
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B284">
         <v>1994</v>
@@ -8236,7 +8271,7 @@
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="B285">
         <v>1994</v>
@@ -8286,7 +8321,7 @@
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B289">
         <v>1994</v>
@@ -8316,7 +8351,7 @@
         <v>1995</v>
       </c>
       <c r="C291" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="D291" t="s">
         <v>405</v>
@@ -8336,7 +8371,7 @@
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="B293">
         <v>1995</v>
@@ -8350,7 +8385,7 @@
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="B294">
         <v>1995</v>
@@ -8388,7 +8423,7 @@
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="B297">
         <v>1995</v>
@@ -8406,7 +8441,7 @@
         <v>1995</v>
       </c>
       <c r="C298" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="D298" t="s">
         <v>368</v>
@@ -8438,7 +8473,7 @@
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B301">
         <v>1995</v>
@@ -8464,7 +8499,7 @@
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="B303">
         <v>1995</v>
@@ -8490,7 +8525,7 @@
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="B305">
         <v>1996</v>
@@ -8504,7 +8539,7 @@
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="B306">
         <v>1996</v>
@@ -8518,7 +8553,7 @@
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B307">
         <v>1996</v>
@@ -8544,7 +8579,7 @@
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="B309">
         <v>1996</v>
@@ -8654,7 +8689,7 @@
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="B318">
         <v>1997</v>
@@ -8672,7 +8707,7 @@
         <v>1997</v>
       </c>
       <c r="C319" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="D319" t="s">
         <v>444</v>
@@ -8699,7 +8734,7 @@
         <v>447</v>
       </c>
       <c r="D321" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.2">
@@ -8824,7 +8859,7 @@
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="B332">
         <v>1998</v>
@@ -8850,7 +8885,7 @@
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="B334">
         <v>1998</v>
@@ -8924,7 +8959,7 @@
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B340">
         <v>1999</v>
@@ -8938,7 +8973,7 @@
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="B341">
         <v>1999</v>
@@ -8952,7 +8987,7 @@
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B342">
         <v>1999</v>
@@ -8966,7 +9001,7 @@
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B343">
         <v>1999</v>
@@ -9044,10 +9079,10 @@
         <v>1999</v>
       </c>
       <c r="C349" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="D349" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.2">
@@ -9064,7 +9099,7 @@
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="B351">
         <v>2000</v>
@@ -9126,7 +9161,7 @@
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="B356">
         <v>2000</v>
@@ -9152,13 +9187,13 @@
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B358">
         <v>2000</v>
       </c>
       <c r="C358" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="D358" t="s">
         <v>499</v>
@@ -9178,7 +9213,7 @@
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="B360">
         <v>2000</v>
@@ -9192,7 +9227,7 @@
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="B361">
         <v>2000</v>
@@ -9209,7 +9244,7 @@
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="B362">
         <v>2000</v>
@@ -9223,7 +9258,7 @@
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="B363">
         <v>2000</v>
@@ -9237,7 +9272,7 @@
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B364">
         <v>2000</v>
@@ -9263,13 +9298,13 @@
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="B366">
         <v>2000</v>
       </c>
       <c r="C366" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
       <c r="D366" t="s">
         <v>408</v>
@@ -9313,7 +9348,7 @@
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="B370">
         <v>2001</v>
@@ -9375,7 +9410,7 @@
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B375">
         <v>2001</v>
@@ -9389,7 +9424,7 @@
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B376">
         <v>2001</v>
@@ -9403,7 +9438,7 @@
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="B377">
         <v>2001</v>
@@ -9477,7 +9512,7 @@
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B383">
         <v>2002</v>
@@ -9527,7 +9562,7 @@
     </row>
     <row r="387" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B387">
         <v>2002</v>
@@ -9565,7 +9600,7 @@
     </row>
     <row r="390" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B390">
         <v>2002</v>
@@ -9591,7 +9626,7 @@
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="B392">
         <v>2002</v>
@@ -9645,7 +9680,7 @@
         <v>2003</v>
       </c>
       <c r="C396" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="D396" t="s">
         <v>554</v>
@@ -9653,7 +9688,7 @@
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B397">
         <v>2003</v>
@@ -9775,7 +9810,7 @@
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B407">
         <v>2003</v>
@@ -9789,7 +9824,7 @@
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B408">
         <v>2003</v>
@@ -9810,7 +9845,7 @@
         <v>570</v>
       </c>
       <c r="D409" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.2">
@@ -9899,7 +9934,7 @@
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B417">
         <v>2004</v>
@@ -9949,7 +9984,7 @@
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B421">
         <v>2004</v>
@@ -9963,7 +9998,7 @@
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B422">
         <v>2004</v>
@@ -9977,7 +10012,7 @@
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B423">
         <v>2004</v>
@@ -10003,7 +10038,7 @@
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B425">
         <v>2004</v>
@@ -10173,7 +10208,7 @@
     </row>
     <row r="439" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B439">
         <v>2005</v>
@@ -10187,7 +10222,7 @@
     </row>
     <row r="440" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A440" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B440">
         <v>2005</v>
@@ -10237,7 +10272,7 @@
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B444">
         <v>2005</v>
@@ -10267,7 +10302,7 @@
         <v>2005</v>
       </c>
       <c r="C446" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="D446" t="s">
         <v>621</v>
@@ -10314,7 +10349,7 @@
     </row>
     <row r="450" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="B450">
         <v>2005</v>
@@ -10328,7 +10363,7 @@
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B451">
         <v>2005</v>
@@ -10354,7 +10389,7 @@
     </row>
     <row r="453" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B453">
         <v>2005</v>
@@ -10380,7 +10415,7 @@
     </row>
     <row r="455" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="B455">
         <v>2006</v>
@@ -10418,7 +10453,7 @@
     </row>
     <row r="458" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A458" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="B458">
         <v>2006</v>
@@ -10432,7 +10467,7 @@
     </row>
     <row r="459" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A459" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B459">
         <v>2006</v>
@@ -10542,7 +10577,7 @@
     </row>
     <row r="468" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A468" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B468">
         <v>2006</v>
@@ -10592,7 +10627,7 @@
     </row>
     <row r="472" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A472" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B472">
         <v>2007</v>
@@ -10606,7 +10641,7 @@
     </row>
     <row r="473" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A473" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B473">
         <v>2007</v>
@@ -10620,7 +10655,7 @@
     </row>
     <row r="474" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A474" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="B474">
         <v>2007</v>
@@ -10641,7 +10676,7 @@
         <v>664</v>
       </c>
       <c r="D475" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="E475" t="s">
         <v>665</v>
@@ -10661,7 +10696,7 @@
     </row>
     <row r="477" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="B477">
         <v>2007</v>
@@ -10670,7 +10705,7 @@
         <v>667</v>
       </c>
       <c r="D477" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="478" spans="1:5" x14ac:dyDescent="0.2">
@@ -10687,7 +10722,7 @@
     </row>
     <row r="479" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A479" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B479">
         <v>2007</v>
@@ -10809,7 +10844,7 @@
     </row>
     <row r="489" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A489" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="B489">
         <v>2007</v>
@@ -10919,7 +10954,7 @@
     </row>
     <row r="498" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A498" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="B498">
         <v>2008</v>
@@ -10933,7 +10968,7 @@
     </row>
     <row r="499" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A499" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B499">
         <v>2008</v>
@@ -10947,7 +10982,7 @@
     </row>
     <row r="500" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A500" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B500">
         <v>2008</v>
@@ -10961,7 +10996,7 @@
     </row>
     <row r="501" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A501" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B501">
         <v>2008</v>
@@ -11143,7 +11178,7 @@
     </row>
     <row r="516" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A516" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B516">
         <v>2009</v>
@@ -11157,7 +11192,7 @@
     </row>
     <row r="517" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A517" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B517">
         <v>2009</v>
@@ -11183,7 +11218,7 @@
     </row>
     <row r="519" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A519" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="B519">
         <v>2009</v>
@@ -11224,7 +11259,7 @@
     </row>
     <row r="522" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A522" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="B522">
         <v>2009</v>
@@ -11250,7 +11285,7 @@
     </row>
     <row r="524" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A524" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B524">
         <v>2009</v>
@@ -11264,7 +11299,7 @@
     </row>
     <row r="525" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A525" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B525">
         <v>2009</v>
@@ -11350,7 +11385,7 @@
     </row>
     <row r="532" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A532" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B532">
         <v>2009</v>
@@ -11523,7 +11558,7 @@
     </row>
     <row r="546" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A546" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B546">
         <v>2010</v>
@@ -11541,7 +11576,7 @@
         <v>2010</v>
       </c>
       <c r="C547" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="D547" t="s">
         <v>775</v>
@@ -11561,7 +11596,7 @@
     </row>
     <row r="549" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B549">
         <v>2010</v>
@@ -11647,7 +11682,7 @@
     </row>
     <row r="556" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B556">
         <v>2010</v>
@@ -11673,7 +11708,7 @@
     </row>
     <row r="558" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="B558">
         <v>2010</v>
@@ -11687,7 +11722,7 @@
     </row>
     <row r="559" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B559">
         <v>2010</v>
@@ -11713,7 +11748,7 @@
     </row>
     <row r="561" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A561" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B561">
         <v>2011</v>
@@ -11763,7 +11798,7 @@
     </row>
     <row r="565" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A565" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B565">
         <v>2011</v>
@@ -11837,7 +11872,7 @@
     </row>
     <row r="571" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A571" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B571">
         <v>2011</v>
@@ -11974,7 +12009,7 @@
     </row>
     <row r="582" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A582" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B582">
         <v>2011</v>
@@ -12012,7 +12047,7 @@
     </row>
     <row r="585" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A585" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B585">
         <v>2012</v>
@@ -12062,7 +12097,7 @@
     </row>
     <row r="589" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A589" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="B589">
         <v>2012</v>
@@ -12148,7 +12183,7 @@
     </row>
     <row r="596" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A596" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="B596">
         <v>2012</v>
@@ -12186,7 +12221,7 @@
     </row>
     <row r="599" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A599" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="B599">
         <v>2012</v>
@@ -12344,13 +12379,13 @@
     </row>
     <row r="612" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A612" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="B612">
         <v>1973</v>
       </c>
       <c r="C612" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="D612" t="s">
         <v>98</v>
@@ -12449,7 +12484,7 @@
         <v>882</v>
       </c>
       <c r="D620" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="621" spans="1:4" x14ac:dyDescent="0.2">
@@ -12458,7 +12493,7 @@
         <v>2013</v>
       </c>
       <c r="C621" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="D621" t="s">
         <v>883</v>
@@ -12502,7 +12537,7 @@
     </row>
     <row r="625" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A625" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B625">
         <v>2013</v>
@@ -12516,7 +12551,7 @@
     </row>
     <row r="626" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A626" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="B626">
         <v>2013</v>
@@ -12530,7 +12565,7 @@
     </row>
     <row r="627" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A627" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="B627">
         <v>2013</v>
@@ -12568,7 +12603,7 @@
     </row>
     <row r="630" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A630" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="B630">
         <v>2013</v>
@@ -12582,7 +12617,7 @@
     </row>
     <row r="631" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A631" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B631">
         <v>2013</v>
@@ -12644,30 +12679,30 @@
     </row>
     <row r="636" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A636" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="B636">
         <v>1956</v>
       </c>
       <c r="C636" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="D636" t="s">
         <v>905</v>
       </c>
     </row>
-    <row r="637" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A637" t="s">
-        <v>1311</v>
-      </c>
-      <c r="B637">
-        <v>2014</v>
-      </c>
-      <c r="C637" t="s">
+    <row r="637" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A637" s="3" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B637" s="3">
+        <v>1958</v>
+      </c>
+      <c r="C637" s="3" t="s">
+        <v>1387</v>
+      </c>
+      <c r="D637" s="3" t="s">
         <v>906</v>
-      </c>
-      <c r="D637" t="s">
-        <v>907</v>
       </c>
     </row>
     <row r="638" spans="1:4" x14ac:dyDescent="0.2">
@@ -12676,7 +12711,7 @@
         <v>2014</v>
       </c>
       <c r="C638" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D638" t="s">
         <v>801</v>
@@ -12688,10 +12723,10 @@
         <v>2014</v>
       </c>
       <c r="C639" t="s">
+        <v>908</v>
+      </c>
+      <c r="D639" t="s">
         <v>909</v>
-      </c>
-      <c r="D639" t="s">
-        <v>910</v>
       </c>
     </row>
     <row r="640" spans="1:4" x14ac:dyDescent="0.2">
@@ -12700,10 +12735,10 @@
         <v>2014</v>
       </c>
       <c r="C640" t="s">
+        <v>910</v>
+      </c>
+      <c r="D640" t="s">
         <v>911</v>
-      </c>
-      <c r="D640" t="s">
-        <v>912</v>
       </c>
     </row>
     <row r="641" spans="1:5" x14ac:dyDescent="0.2">
@@ -12712,41 +12747,41 @@
         <v>2014</v>
       </c>
       <c r="C641" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="D641" t="s">
+        <v>912</v>
+      </c>
+      <c r="E641" t="s">
         <v>913</v>
-      </c>
-      <c r="E641" t="s">
-        <v>914</v>
       </c>
     </row>
     <row r="642" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A642" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B642">
         <v>2014</v>
       </c>
       <c r="C642" t="s">
+        <v>916</v>
+      </c>
+      <c r="D642" t="s">
         <v>917</v>
-      </c>
-      <c r="D642" t="s">
-        <v>918</v>
       </c>
     </row>
     <row r="643" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A643" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B643">
         <v>2014</v>
       </c>
       <c r="C643" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="D643" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="644" spans="1:5" x14ac:dyDescent="0.2">
@@ -12755,21 +12790,21 @@
         <v>2014</v>
       </c>
       <c r="C644" t="s">
+        <v>919</v>
+      </c>
+      <c r="D644" t="s">
         <v>920</v>
-      </c>
-      <c r="D644" t="s">
-        <v>921</v>
       </c>
     </row>
     <row r="645" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A645" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="B645">
         <v>2014</v>
       </c>
       <c r="C645" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="D645" t="s">
         <v>833</v>
@@ -12777,27 +12812,27 @@
     </row>
     <row r="646" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A646" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="B646">
         <v>2014</v>
       </c>
       <c r="C646" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="D646" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="647" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A647" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="B647">
         <v>1970</v>
       </c>
       <c r="C647" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D647" t="s">
         <v>21</v>
@@ -12805,13 +12840,13 @@
     </row>
     <row r="648" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A648" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B648">
         <v>2014</v>
       </c>
       <c r="C648" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="D648" t="s">
         <v>54</v>
@@ -12823,7 +12858,7 @@
         <v>2014</v>
       </c>
       <c r="C649" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="D649" t="s">
         <v>767</v>
@@ -12835,7 +12870,7 @@
         <v>2014</v>
       </c>
       <c r="C650" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="D650" t="s">
         <v>826</v>
@@ -12847,7 +12882,7 @@
         <v>2014</v>
       </c>
       <c r="C651" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="D651" t="s">
         <v>54</v>
@@ -12859,21 +12894,21 @@
         <v>2014</v>
       </c>
       <c r="C652" t="s">
+        <v>928</v>
+      </c>
+      <c r="D652" t="s">
         <v>929</v>
-      </c>
-      <c r="D652" t="s">
-        <v>930</v>
       </c>
     </row>
     <row r="653" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A653" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B653">
         <v>2014</v>
       </c>
       <c r="C653" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="D653" t="s">
         <v>813</v>
@@ -12881,27 +12916,27 @@
     </row>
     <row r="654" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A654" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B654">
         <v>2014</v>
       </c>
       <c r="C654" t="s">
+        <v>931</v>
+      </c>
+      <c r="D654" t="s">
         <v>932</v>
-      </c>
-      <c r="D654" t="s">
-        <v>933</v>
       </c>
     </row>
     <row r="655" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A655" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="B655">
         <v>2014</v>
       </c>
       <c r="C655" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="D655" t="s">
         <v>356</v>
@@ -12913,10 +12948,10 @@
         <v>2014</v>
       </c>
       <c r="C656" t="s">
+        <v>934</v>
+      </c>
+      <c r="D656" t="s">
         <v>935</v>
-      </c>
-      <c r="D656" t="s">
-        <v>936</v>
       </c>
     </row>
     <row r="657" spans="1:4" x14ac:dyDescent="0.2">
@@ -12925,7 +12960,7 @@
         <v>2014</v>
       </c>
       <c r="C657" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="D657" t="s">
         <v>536</v>
@@ -12937,7 +12972,7 @@
         <v>2014</v>
       </c>
       <c r="C658" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="D658" t="s">
         <v>760</v>
@@ -12949,10 +12984,10 @@
         <v>2014</v>
       </c>
       <c r="C659" t="s">
+        <v>938</v>
+      </c>
+      <c r="D659" t="s">
         <v>939</v>
-      </c>
-      <c r="D659" t="s">
-        <v>940</v>
       </c>
     </row>
     <row r="660" spans="1:4" x14ac:dyDescent="0.2">
@@ -12961,7 +12996,7 @@
         <v>2014</v>
       </c>
       <c r="C660" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="D660" t="s">
         <v>515</v>
@@ -12973,7 +13008,7 @@
         <v>2014</v>
       </c>
       <c r="C661" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="D661" t="s">
         <v>606</v>
@@ -12985,10 +13020,10 @@
         <v>2015</v>
       </c>
       <c r="C662" t="s">
+        <v>942</v>
+      </c>
+      <c r="D662" t="s">
         <v>943</v>
-      </c>
-      <c r="D662" t="s">
-        <v>944</v>
       </c>
     </row>
     <row r="663" spans="1:4" x14ac:dyDescent="0.2">
@@ -12997,7 +13032,7 @@
         <v>2015</v>
       </c>
       <c r="C663" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="D663" t="s">
         <v>444</v>
@@ -13009,7 +13044,7 @@
         <v>2015</v>
       </c>
       <c r="C664" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="D664" t="s">
         <v>14</v>
@@ -13021,7 +13056,7 @@
         <v>2015</v>
       </c>
       <c r="C665" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="D665" t="s">
         <v>5</v>
@@ -13033,7 +13068,7 @@
         <v>2015</v>
       </c>
       <c r="C666" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="D666" t="s">
         <v>614</v>
@@ -13045,10 +13080,10 @@
         <v>2015</v>
       </c>
       <c r="C667" t="s">
+        <v>948</v>
+      </c>
+      <c r="D667" t="s">
         <v>949</v>
-      </c>
-      <c r="D667" t="s">
-        <v>950</v>
       </c>
     </row>
     <row r="668" spans="1:4" x14ac:dyDescent="0.2">
@@ -13057,10 +13092,10 @@
         <v>2015</v>
       </c>
       <c r="C668" t="s">
+        <v>950</v>
+      </c>
+      <c r="D668" t="s">
         <v>951</v>
-      </c>
-      <c r="D668" t="s">
-        <v>952</v>
       </c>
     </row>
     <row r="669" spans="1:4" x14ac:dyDescent="0.2">
@@ -13069,24 +13104,24 @@
         <v>2015</v>
       </c>
       <c r="C669" t="s">
+        <v>952</v>
+      </c>
+      <c r="D669" t="s">
         <v>953</v>
-      </c>
-      <c r="D669" t="s">
-        <v>954</v>
       </c>
     </row>
     <row r="670" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A670" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="B670">
         <v>2015</v>
       </c>
       <c r="C670" t="s">
+        <v>954</v>
+      </c>
+      <c r="D670" t="s">
         <v>955</v>
-      </c>
-      <c r="D670" t="s">
-        <v>956</v>
       </c>
     </row>
     <row r="671" spans="1:4" x14ac:dyDescent="0.2">
@@ -13095,7 +13130,7 @@
         <v>2015</v>
       </c>
       <c r="C671" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="D671" t="s">
         <v>554</v>
@@ -13107,7 +13142,7 @@
         <v>2015</v>
       </c>
       <c r="C672" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="D672" t="s">
         <v>769</v>
@@ -13119,41 +13154,41 @@
         <v>2015</v>
       </c>
       <c r="C673" t="s">
+        <v>958</v>
+      </c>
+      <c r="D673" t="s">
         <v>959</v>
       </c>
-      <c r="D673" t="s">
-        <v>960</v>
-      </c>
       <c r="E673" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="674" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A674" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="B674">
         <v>2014</v>
       </c>
       <c r="C674" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="D674" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="675" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A675" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="B675">
         <v>2015</v>
       </c>
       <c r="C675" t="s">
+        <v>961</v>
+      </c>
+      <c r="D675" t="s">
         <v>962</v>
-      </c>
-      <c r="D675" t="s">
-        <v>963</v>
       </c>
     </row>
     <row r="676" spans="1:5" x14ac:dyDescent="0.2">
@@ -13162,10 +13197,10 @@
         <v>2015</v>
       </c>
       <c r="C676" t="s">
+        <v>963</v>
+      </c>
+      <c r="D676" t="s">
         <v>964</v>
-      </c>
-      <c r="D676" t="s">
-        <v>965</v>
       </c>
     </row>
     <row r="677" spans="1:5" x14ac:dyDescent="0.2">
@@ -13174,24 +13209,24 @@
         <v>2015</v>
       </c>
       <c r="C677" t="s">
+        <v>965</v>
+      </c>
+      <c r="D677" t="s">
         <v>966</v>
-      </c>
-      <c r="D677" t="s">
-        <v>967</v>
       </c>
     </row>
     <row r="678" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A678" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="B678">
         <v>2015</v>
       </c>
       <c r="C678" t="s">
+        <v>967</v>
+      </c>
+      <c r="D678" t="s">
         <v>968</v>
-      </c>
-      <c r="D678" t="s">
-        <v>969</v>
       </c>
     </row>
     <row r="679" spans="1:5" x14ac:dyDescent="0.2">
@@ -13200,13 +13235,13 @@
         <v>2015</v>
       </c>
       <c r="C679" t="s">
+        <v>969</v>
+      </c>
+      <c r="D679" t="s">
+        <v>969</v>
+      </c>
+      <c r="E679" t="s">
         <v>970</v>
-      </c>
-      <c r="D679" t="s">
-        <v>970</v>
-      </c>
-      <c r="E679" t="s">
-        <v>971</v>
       </c>
     </row>
     <row r="680" spans="1:5" x14ac:dyDescent="0.2">
@@ -13215,7 +13250,7 @@
         <v>2015</v>
       </c>
       <c r="C680" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="D680" t="s">
         <v>773</v>
@@ -13230,10 +13265,10 @@
         <v>2015</v>
       </c>
       <c r="C681" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="D681" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="682" spans="1:5" x14ac:dyDescent="0.2">
@@ -13242,10 +13277,10 @@
         <v>2015</v>
       </c>
       <c r="C682" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="D682" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="683" spans="1:5" x14ac:dyDescent="0.2">
@@ -13254,7 +13289,7 @@
         <v>2015</v>
       </c>
       <c r="C683" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="D683" t="s">
         <v>835</v>
@@ -13266,10 +13301,10 @@
         <v>2015</v>
       </c>
       <c r="C684" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="D684" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="685" spans="1:5" x14ac:dyDescent="0.2">
@@ -13278,7 +13313,7 @@
         <v>2015</v>
       </c>
       <c r="C685" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="D685" t="s">
         <v>483</v>
@@ -13290,7 +13325,7 @@
         <v>2015</v>
       </c>
       <c r="C686" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="D686" t="s">
         <v>430</v>
@@ -13298,19 +13333,19 @@
     </row>
     <row r="687" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A687" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="B687">
         <v>2015</v>
       </c>
       <c r="C687" t="s">
+        <v>978</v>
+      </c>
+      <c r="D687" t="s">
         <v>979</v>
       </c>
-      <c r="D687" t="s">
+      <c r="E687" t="s">
         <v>980</v>
-      </c>
-      <c r="E687" t="s">
-        <v>981</v>
       </c>
     </row>
     <row r="688" spans="1:5" x14ac:dyDescent="0.2">
@@ -13319,7 +13354,7 @@
         <v>2015</v>
       </c>
       <c r="C688" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="D688" t="s">
         <v>787</v>
@@ -13327,41 +13362,41 @@
     </row>
     <row r="689" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A689" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="B689">
         <v>2015</v>
       </c>
       <c r="C689" t="s">
+        <v>982</v>
+      </c>
+      <c r="D689" t="s">
         <v>983</v>
-      </c>
-      <c r="D689" t="s">
-        <v>984</v>
       </c>
     </row>
     <row r="690" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A690" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B690">
         <v>2015</v>
       </c>
       <c r="C690" t="s">
+        <v>984</v>
+      </c>
+      <c r="D690" t="s">
         <v>985</v>
-      </c>
-      <c r="D690" t="s">
-        <v>986</v>
       </c>
     </row>
     <row r="691" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A691" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="B691">
         <v>2015</v>
       </c>
       <c r="C691" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="D691" t="s">
         <v>819</v>
@@ -13369,13 +13404,13 @@
     </row>
     <row r="692" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A692" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B692">
         <v>2016</v>
       </c>
       <c r="C692" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="D692" t="s">
         <v>700</v>
@@ -13383,13 +13418,13 @@
     </row>
     <row r="693" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A693" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="B693">
         <v>2016</v>
       </c>
       <c r="C693" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="D693" t="s">
         <v>366</v>
@@ -13397,16 +13432,16 @@
     </row>
     <row r="694" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A694" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="B694">
         <v>2016</v>
       </c>
       <c r="C694" t="s">
+        <v>989</v>
+      </c>
+      <c r="D694" t="s">
         <v>990</v>
-      </c>
-      <c r="D694" t="s">
-        <v>991</v>
       </c>
     </row>
     <row r="695" spans="1:4" x14ac:dyDescent="0.2">
@@ -13415,7 +13450,7 @@
         <v>2016</v>
       </c>
       <c r="C695" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="D695" t="s">
         <v>897</v>
@@ -13427,7 +13462,7 @@
         <v>2016</v>
       </c>
       <c r="C696" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="D696" t="s">
         <v>662</v>
@@ -13439,21 +13474,21 @@
         <v>2016</v>
       </c>
       <c r="C697" t="s">
+        <v>993</v>
+      </c>
+      <c r="D697" t="s">
         <v>994</v>
-      </c>
-      <c r="D697" t="s">
-        <v>995</v>
       </c>
     </row>
     <row r="698" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A698" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B698">
         <v>2016</v>
       </c>
       <c r="C698" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="D698" t="s">
         <v>126</v>
@@ -13465,10 +13500,10 @@
         <v>2016</v>
       </c>
       <c r="C699" t="s">
+        <v>996</v>
+      </c>
+      <c r="D699" t="s">
         <v>997</v>
-      </c>
-      <c r="D699" t="s">
-        <v>998</v>
       </c>
     </row>
     <row r="700" spans="1:4" x14ac:dyDescent="0.2">
@@ -13477,21 +13512,21 @@
         <v>2016</v>
       </c>
       <c r="C700" t="s">
+        <v>998</v>
+      </c>
+      <c r="D700" t="s">
         <v>999</v>
-      </c>
-      <c r="D700" t="s">
-        <v>1000</v>
       </c>
     </row>
     <row r="701" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A701" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B701">
         <v>2016</v>
       </c>
       <c r="C701" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="D701" t="s">
         <v>810</v>
@@ -13503,7 +13538,7 @@
         <v>2016</v>
       </c>
       <c r="C702" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="D702" t="s">
         <v>418</v>
@@ -13515,7 +13550,7 @@
         <v>2016</v>
       </c>
       <c r="C703" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="D703" t="s">
         <v>366</v>
@@ -13527,10 +13562,10 @@
         <v>2016</v>
       </c>
       <c r="C704" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="D704" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="705" spans="1:5" x14ac:dyDescent="0.2">
@@ -13539,10 +13574,10 @@
         <v>2016</v>
       </c>
       <c r="C705" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D705" t="s">
         <v>1005</v>
-      </c>
-      <c r="D705" t="s">
-        <v>1006</v>
       </c>
     </row>
     <row r="706" spans="1:5" x14ac:dyDescent="0.2">
@@ -13551,10 +13586,10 @@
         <v>2016</v>
       </c>
       <c r="C706" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D706" t="s">
         <v>1007</v>
-      </c>
-      <c r="D706" t="s">
-        <v>1008</v>
       </c>
     </row>
     <row r="707" spans="1:5" x14ac:dyDescent="0.2">
@@ -13563,13 +13598,13 @@
         <v>2016</v>
       </c>
       <c r="C707" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D707" t="s">
         <v>1009</v>
       </c>
-      <c r="D707" t="s">
+      <c r="E707" t="s">
         <v>1010</v>
-      </c>
-      <c r="E707" t="s">
-        <v>1011</v>
       </c>
     </row>
     <row r="708" spans="1:5" x14ac:dyDescent="0.2">
@@ -13578,10 +13613,10 @@
         <v>2016</v>
       </c>
       <c r="C708" t="s">
+        <v>1011</v>
+      </c>
+      <c r="D708" t="s">
         <v>1012</v>
-      </c>
-      <c r="D708" t="s">
-        <v>1013</v>
       </c>
     </row>
     <row r="709" spans="1:5" x14ac:dyDescent="0.2">
@@ -13590,10 +13625,10 @@
         <v>2016</v>
       </c>
       <c r="C709" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="D709" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="710" spans="1:5" x14ac:dyDescent="0.2">
@@ -13602,10 +13637,10 @@
         <v>2016</v>
       </c>
       <c r="C710" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="D710" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="711" spans="1:5" x14ac:dyDescent="0.2">
@@ -13614,10 +13649,10 @@
         <v>2016</v>
       </c>
       <c r="C711" t="s">
+        <v>1015</v>
+      </c>
+      <c r="D711" t="s">
         <v>1016</v>
-      </c>
-      <c r="D711" t="s">
-        <v>1017</v>
       </c>
     </row>
     <row r="712" spans="1:5" x14ac:dyDescent="0.2">
@@ -13626,7 +13661,7 @@
         <v>2016</v>
       </c>
       <c r="C712" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="D712" t="s">
         <v>430</v>
@@ -13638,7 +13673,7 @@
         <v>2016</v>
       </c>
       <c r="C713" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="D713" t="s">
         <v>712</v>
@@ -13650,10 +13685,10 @@
         <v>2016</v>
       </c>
       <c r="C714" t="s">
+        <v>1019</v>
+      </c>
+      <c r="D714" t="s">
         <v>1020</v>
-      </c>
-      <c r="D714" t="s">
-        <v>1021</v>
       </c>
     </row>
     <row r="715" spans="1:5" x14ac:dyDescent="0.2">
@@ -13662,7 +13697,7 @@
         <v>2016</v>
       </c>
       <c r="C715" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="D715" t="s">
         <v>792</v>
@@ -13674,7 +13709,7 @@
         <v>2016</v>
       </c>
       <c r="C716" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="D716" t="s">
         <v>312</v>
@@ -13686,21 +13721,21 @@
         <v>2016</v>
       </c>
       <c r="C717" t="s">
+        <v>1023</v>
+      </c>
+      <c r="D717" t="s">
         <v>1024</v>
-      </c>
-      <c r="D717" t="s">
-        <v>1025</v>
       </c>
     </row>
     <row r="718" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A718" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="B718">
         <v>2016</v>
       </c>
       <c r="C718" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="D718" t="s">
         <v>147</v>
@@ -13708,16 +13743,16 @@
     </row>
     <row r="719" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A719" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B719">
         <v>2016</v>
       </c>
       <c r="C719" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="D719" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="720" spans="1:5" x14ac:dyDescent="0.2">
@@ -13726,21 +13761,21 @@
         <v>2016</v>
       </c>
       <c r="C720" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D720" t="s">
         <v>1028</v>
-      </c>
-      <c r="D720" t="s">
-        <v>1029</v>
       </c>
     </row>
     <row r="721" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A721" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="B721">
         <v>2016</v>
       </c>
       <c r="C721" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="D721" t="s">
         <v>893</v>
@@ -13752,7 +13787,7 @@
         <v>2016</v>
       </c>
       <c r="C722" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="D722" t="s">
         <v>505</v>
@@ -13760,13 +13795,13 @@
     </row>
     <row r="723" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A723" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B723">
         <v>2016</v>
       </c>
       <c r="C723" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="D723" t="s">
         <v>54</v>
@@ -13778,7 +13813,7 @@
         <v>2017</v>
       </c>
       <c r="C724" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="D724" t="s">
         <v>77</v>
@@ -13790,10 +13825,10 @@
         <v>2017</v>
       </c>
       <c r="C725" t="s">
+        <v>1033</v>
+      </c>
+      <c r="D725" t="s">
         <v>1034</v>
-      </c>
-      <c r="D725" t="s">
-        <v>1035</v>
       </c>
     </row>
     <row r="726" spans="1:4" x14ac:dyDescent="0.2">
@@ -13802,7 +13837,7 @@
         <v>2017</v>
       </c>
       <c r="C726" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="D726" t="s">
         <v>767</v>
@@ -13814,10 +13849,10 @@
         <v>2017</v>
       </c>
       <c r="C727" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D727" t="s">
         <v>1037</v>
-      </c>
-      <c r="D727" t="s">
-        <v>1038</v>
       </c>
     </row>
     <row r="728" spans="1:4" x14ac:dyDescent="0.2">
@@ -13826,7 +13861,7 @@
         <v>2017</v>
       </c>
       <c r="C728" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="D728" t="s">
         <v>592</v>
@@ -13838,38 +13873,38 @@
         <v>2017</v>
       </c>
       <c r="C729" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D729" t="s">
         <v>1040</v>
-      </c>
-      <c r="D729" t="s">
-        <v>1041</v>
       </c>
     </row>
     <row r="730" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A730" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="B730">
         <v>2017</v>
       </c>
       <c r="C730" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="D730" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="731" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A731" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="B731">
         <v>2017</v>
       </c>
       <c r="C731" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="D731" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="732" spans="1:4" x14ac:dyDescent="0.2">
@@ -13878,21 +13913,21 @@
         <v>2017</v>
       </c>
       <c r="C732" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="D732" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="733" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A733" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B733">
         <v>2017</v>
       </c>
       <c r="C733" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="D733" t="s">
         <v>614</v>
@@ -13904,7 +13939,7 @@
         <v>2017</v>
       </c>
       <c r="C734" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="D734" t="s">
         <v>698</v>
@@ -13916,10 +13951,10 @@
         <v>2017</v>
       </c>
       <c r="C735" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="D735" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="736" spans="1:4" x14ac:dyDescent="0.2">
@@ -13928,7 +13963,7 @@
         <v>2017</v>
       </c>
       <c r="C736" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="D736" t="s">
         <v>588</v>
@@ -13940,7 +13975,7 @@
         <v>2017</v>
       </c>
       <c r="C737" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="D737" t="s">
         <v>539</v>
@@ -13952,7 +13987,7 @@
         <v>2017</v>
       </c>
       <c r="C738" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="D738" t="s">
         <v>902</v>
@@ -13964,7 +13999,7 @@
         <v>2017</v>
       </c>
       <c r="C739" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="D739" t="s">
         <v>366</v>
@@ -13976,7 +14011,7 @@
         <v>2017</v>
       </c>
       <c r="C740" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="D740" t="s">
         <v>753</v>
@@ -13984,13 +14019,13 @@
     </row>
     <row r="741" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A741" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B741">
         <v>1977</v>
       </c>
       <c r="C741" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="D741" t="s">
         <v>160</v>
@@ -14002,10 +14037,10 @@
         <v>2017</v>
       </c>
       <c r="C742" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D742" t="s">
         <v>1053</v>
-      </c>
-      <c r="D742" t="s">
-        <v>1054</v>
       </c>
     </row>
     <row r="743" spans="1:5" x14ac:dyDescent="0.2">
@@ -14014,7 +14049,7 @@
         <v>2017</v>
       </c>
       <c r="C743" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="D743" t="s">
         <v>444</v>
@@ -14026,7 +14061,7 @@
         <v>2017</v>
       </c>
       <c r="C744" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="D744" t="s">
         <v>366</v>
@@ -14034,13 +14069,13 @@
     </row>
     <row r="745" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A745" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="B745">
         <v>2017</v>
       </c>
       <c r="C745" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="D745" t="s">
         <v>753</v>
@@ -14052,7 +14087,7 @@
         <v>2017</v>
       </c>
       <c r="C746" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="D746" t="s">
         <v>747</v>
@@ -14064,27 +14099,27 @@
         <v>2017</v>
       </c>
       <c r="C747" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D747" t="s">
         <v>1059</v>
       </c>
-      <c r="D747" t="s">
-        <v>1060</v>
-      </c>
       <c r="E747" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="748" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A748" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="B748">
         <v>2017</v>
       </c>
       <c r="C748" t="s">
+        <v>1060</v>
+      </c>
+      <c r="D748" t="s">
         <v>1061</v>
-      </c>
-      <c r="D748" t="s">
-        <v>1062</v>
       </c>
     </row>
     <row r="749" spans="1:5" x14ac:dyDescent="0.2">
@@ -14093,10 +14128,10 @@
         <v>2017</v>
       </c>
       <c r="C749" t="s">
+        <v>1062</v>
+      </c>
+      <c r="D749" t="s">
         <v>1063</v>
-      </c>
-      <c r="D749" t="s">
-        <v>1064</v>
       </c>
     </row>
     <row r="750" spans="1:5" x14ac:dyDescent="0.2">
@@ -14105,7 +14140,7 @@
         <v>2017</v>
       </c>
       <c r="C750" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="D750" t="s">
         <v>831</v>
@@ -14117,10 +14152,10 @@
         <v>2017</v>
       </c>
       <c r="C751" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D751" t="s">
         <v>1066</v>
-      </c>
-      <c r="D751" t="s">
-        <v>1067</v>
       </c>
     </row>
     <row r="752" spans="1:5" x14ac:dyDescent="0.2">
@@ -14129,7 +14164,7 @@
         <v>2017</v>
       </c>
       <c r="C752" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="D752" t="s">
         <v>588</v>
@@ -14141,7 +14176,7 @@
         <v>2017</v>
       </c>
       <c r="C753" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="D753" t="s">
         <v>531</v>
@@ -14153,10 +14188,10 @@
         <v>2017</v>
       </c>
       <c r="C754" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="D754" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="755" spans="1:4" x14ac:dyDescent="0.2">
@@ -14165,7 +14200,7 @@
         <v>2017</v>
       </c>
       <c r="C755" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="D755" t="s">
         <v>813</v>
@@ -14177,10 +14212,10 @@
         <v>2017</v>
       </c>
       <c r="C756" t="s">
+        <v>1070</v>
+      </c>
+      <c r="D756" t="s">
         <v>1071</v>
-      </c>
-      <c r="D756" t="s">
-        <v>1072</v>
       </c>
     </row>
     <row r="757" spans="1:4" x14ac:dyDescent="0.2">
@@ -14189,10 +14224,10 @@
         <v>2017</v>
       </c>
       <c r="C757" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D757" t="s">
         <v>1073</v>
-      </c>
-      <c r="D757" t="s">
-        <v>1074</v>
       </c>
     </row>
     <row r="758" spans="1:4" x14ac:dyDescent="0.2">
@@ -14201,7 +14236,7 @@
         <v>2017</v>
       </c>
       <c r="C758" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="D758" t="s">
         <v>606</v>
@@ -14209,13 +14244,13 @@
     </row>
     <row r="759" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A759" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B759">
         <v>1968</v>
       </c>
       <c r="C759" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="D759" t="s">
         <v>77</v>
@@ -14223,16 +14258,16 @@
     </row>
     <row r="760" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A760" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="B760">
         <v>2018</v>
       </c>
       <c r="C760" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D760" t="s">
         <v>1076</v>
-      </c>
-      <c r="D760" t="s">
-        <v>1077</v>
       </c>
     </row>
     <row r="761" spans="1:4" x14ac:dyDescent="0.2">
@@ -14241,7 +14276,7 @@
         <v>2018</v>
       </c>
       <c r="C761" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="D761" t="s">
         <v>100</v>
@@ -14256,7 +14291,7 @@
         <v>7</v>
       </c>
       <c r="D762" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="763" spans="1:4" x14ac:dyDescent="0.2">
@@ -14265,10 +14300,10 @@
         <v>2018</v>
       </c>
       <c r="C763" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D763" t="s">
         <v>1079</v>
-      </c>
-      <c r="D763" t="s">
-        <v>1080</v>
       </c>
     </row>
     <row r="764" spans="1:4" x14ac:dyDescent="0.2">
@@ -14277,7 +14312,7 @@
         <v>2018</v>
       </c>
       <c r="C764" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="D764" t="s">
         <v>819</v>
@@ -14285,13 +14320,13 @@
     </row>
     <row r="765" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A765" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B765">
         <v>2018</v>
       </c>
       <c r="C765" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="D765" t="s">
         <v>531</v>
@@ -14299,30 +14334,30 @@
     </row>
     <row r="766" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A766" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="B766">
-        <v>1947</v>
+        <v>1977</v>
       </c>
       <c r="C766" t="s">
-        <v>1265</v>
+        <v>1388</v>
       </c>
       <c r="D766" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="767" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A767" s="2" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B767" s="2">
         <v>2018</v>
       </c>
       <c r="C767" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D767" s="2" t="s">
         <v>1084</v>
-      </c>
-      <c r="D767" s="2" t="s">
-        <v>1085</v>
       </c>
     </row>
     <row r="768" spans="1:4" x14ac:dyDescent="0.2">
@@ -14331,10 +14366,10 @@
         <v>2018</v>
       </c>
       <c r="C768" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D768" t="s">
         <v>1086</v>
-      </c>
-      <c r="D768" t="s">
-        <v>1087</v>
       </c>
     </row>
     <row r="769" spans="1:5" x14ac:dyDescent="0.2">
@@ -14343,13 +14378,13 @@
         <v>2018</v>
       </c>
       <c r="C769" t="s">
+        <v>1087</v>
+      </c>
+      <c r="D769" t="s">
         <v>1088</v>
       </c>
-      <c r="D769" t="s">
-        <v>1089</v>
-      </c>
       <c r="E769" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="770" spans="1:5" x14ac:dyDescent="0.2">
@@ -14358,7 +14393,7 @@
         <v>2018</v>
       </c>
       <c r="C770" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="D770" t="s">
         <v>826</v>
@@ -14366,16 +14401,16 @@
     </row>
     <row r="771" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A771" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="B771">
         <v>2018</v>
       </c>
       <c r="C771" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D771" t="s">
         <v>1091</v>
-      </c>
-      <c r="D771" t="s">
-        <v>1092</v>
       </c>
     </row>
     <row r="772" spans="1:5" x14ac:dyDescent="0.2">
@@ -14384,10 +14419,10 @@
         <v>2018</v>
       </c>
       <c r="C772" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D772" t="s">
         <v>1093</v>
-      </c>
-      <c r="D772" t="s">
-        <v>1094</v>
       </c>
     </row>
     <row r="773" spans="1:5" x14ac:dyDescent="0.2">
@@ -14396,7 +14431,7 @@
         <v>2018</v>
       </c>
       <c r="C773" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="D773" t="s">
         <v>19</v>
@@ -14408,10 +14443,10 @@
         <v>2018</v>
       </c>
       <c r="C774" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D774" t="s">
         <v>1096</v>
-      </c>
-      <c r="D774" t="s">
-        <v>1097</v>
       </c>
     </row>
     <row r="775" spans="1:5" x14ac:dyDescent="0.2">
@@ -14420,7 +14455,7 @@
         <v>2018</v>
       </c>
       <c r="C775" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="D775" t="s">
         <v>831</v>
@@ -14432,35 +14467,35 @@
         <v>2018</v>
       </c>
       <c r="C776" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D776" t="s">
         <v>1099</v>
-      </c>
-      <c r="D776" t="s">
-        <v>1100</v>
       </c>
     </row>
     <row r="777" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A777" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="B777">
         <v>2018</v>
       </c>
       <c r="C777" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D777" t="s">
         <v>1101</v>
-      </c>
-      <c r="D777" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="778" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A778" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="B778">
         <v>2018</v>
       </c>
       <c r="C778" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="D778" t="s">
         <v>127</v>
@@ -14472,7 +14507,7 @@
         <v>2018</v>
       </c>
       <c r="C779" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="D779" t="s">
         <v>377</v>
@@ -14484,10 +14519,10 @@
         <v>2018</v>
       </c>
       <c r="C780" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D780" t="s">
         <v>1105</v>
-      </c>
-      <c r="D780" t="s">
-        <v>1106</v>
       </c>
     </row>
     <row r="781" spans="1:5" x14ac:dyDescent="0.2">
@@ -14496,7 +14531,7 @@
         <v>2019</v>
       </c>
       <c r="C781" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="D781" t="s">
         <v>656</v>
@@ -14508,10 +14543,10 @@
         <v>2019</v>
       </c>
       <c r="C782" t="s">
+        <v>1107</v>
+      </c>
+      <c r="D782" t="s">
         <v>1108</v>
-      </c>
-      <c r="D782" t="s">
-        <v>1109</v>
       </c>
     </row>
     <row r="783" spans="1:5" x14ac:dyDescent="0.2">
@@ -14520,10 +14555,10 @@
         <v>2019</v>
       </c>
       <c r="C783" t="s">
+        <v>1109</v>
+      </c>
+      <c r="D783" t="s">
         <v>1110</v>
-      </c>
-      <c r="D783" t="s">
-        <v>1111</v>
       </c>
     </row>
     <row r="784" spans="1:5" x14ac:dyDescent="0.2">
@@ -14532,7 +14567,7 @@
         <v>2019</v>
       </c>
       <c r="C784" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="D784" t="s">
         <v>312</v>
@@ -14544,7 +14579,7 @@
         <v>2019</v>
       </c>
       <c r="C785" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="D785" t="s">
         <v>531</v>
@@ -14556,7 +14591,7 @@
         <v>2019</v>
       </c>
       <c r="C786" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="D786" t="s">
         <v>539</v>
@@ -14568,7 +14603,7 @@
         <v>2019</v>
       </c>
       <c r="C787" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="D787" t="s">
         <v>531</v>
@@ -14580,10 +14615,10 @@
         <v>2019</v>
       </c>
       <c r="C788" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="D788" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="789" spans="1:5" x14ac:dyDescent="0.2">
@@ -14592,10 +14627,10 @@
         <v>2019</v>
       </c>
       <c r="C789" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="D789" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="790" spans="1:5" x14ac:dyDescent="0.2">
@@ -14604,10 +14639,10 @@
         <v>2019</v>
       </c>
       <c r="C790" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="D790" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="791" spans="1:5" x14ac:dyDescent="0.2">
@@ -14616,10 +14651,10 @@
         <v>2019</v>
       </c>
       <c r="C791" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="D791" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="792" spans="1:5" x14ac:dyDescent="0.2">
@@ -14628,7 +14663,7 @@
         <v>2019</v>
       </c>
       <c r="C792" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="D792" t="s">
         <v>739</v>
@@ -14640,10 +14675,10 @@
         <v>2019</v>
       </c>
       <c r="C793" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D793" t="s">
         <v>1121</v>
-      </c>
-      <c r="D793" t="s">
-        <v>1122</v>
       </c>
     </row>
     <row r="794" spans="1:5" x14ac:dyDescent="0.2">
@@ -14652,10 +14687,10 @@
         <v>2019</v>
       </c>
       <c r="C794" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="D794" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="795" spans="1:5" x14ac:dyDescent="0.2">
@@ -14664,10 +14699,10 @@
         <v>2019</v>
       </c>
       <c r="C795" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D795" t="s">
         <v>1123</v>
-      </c>
-      <c r="D795" t="s">
-        <v>1124</v>
       </c>
     </row>
     <row r="796" spans="1:5" x14ac:dyDescent="0.2">
@@ -14676,7 +14711,7 @@
         <v>2019</v>
       </c>
       <c r="C796" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="D796" t="s">
         <v>181</v>
@@ -14684,19 +14719,19 @@
     </row>
     <row r="797" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A797" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B797">
         <v>2019</v>
       </c>
       <c r="C797" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="D797" t="s">
         <v>463</v>
       </c>
       <c r="E797" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="798" spans="1:5" x14ac:dyDescent="0.2">
@@ -14705,10 +14740,10 @@
         <v>2019</v>
       </c>
       <c r="C798" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D798" t="s">
         <v>1127</v>
-      </c>
-      <c r="D798" t="s">
-        <v>1128</v>
       </c>
     </row>
     <row r="799" spans="1:5" x14ac:dyDescent="0.2">
@@ -14717,7 +14752,7 @@
         <v>2019</v>
       </c>
       <c r="C799" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="D799" t="s">
         <v>700</v>
@@ -14729,10 +14764,10 @@
         <v>2020</v>
       </c>
       <c r="C800" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D800" t="s">
         <v>1130</v>
-      </c>
-      <c r="D800" t="s">
-        <v>1131</v>
       </c>
     </row>
     <row r="801" spans="1:5" x14ac:dyDescent="0.2">
@@ -14741,7 +14776,7 @@
         <v>2020</v>
       </c>
       <c r="C801" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="D801" t="s">
         <v>418</v>
@@ -14753,7 +14788,7 @@
         <v>2020</v>
       </c>
       <c r="C802" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="D802" t="s">
         <v>549</v>
@@ -14761,16 +14796,16 @@
     </row>
     <row r="803" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A803" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B803">
         <v>2020</v>
       </c>
       <c r="C803" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D803" t="s">
         <v>1134</v>
-      </c>
-      <c r="D803" t="s">
-        <v>1135</v>
       </c>
     </row>
     <row r="804" spans="1:5" x14ac:dyDescent="0.2">
@@ -14779,7 +14814,7 @@
         <v>2020</v>
       </c>
       <c r="C804" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="D804" t="s">
         <v>700</v>
@@ -14791,7 +14826,7 @@
         <v>2020</v>
       </c>
       <c r="C805" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="D805" t="s">
         <v>813</v>
@@ -14803,15 +14838,15 @@
         <v>2020</v>
       </c>
       <c r="C806" t="s">
+        <v>1137</v>
+      </c>
+      <c r="D806" t="s">
         <v>1138</v>
-      </c>
-      <c r="D806" t="s">
-        <v>1139</v>
       </c>
     </row>
     <row r="807" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A807" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="B807">
         <v>2020</v>
@@ -14825,16 +14860,16 @@
     </row>
     <row r="808" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A808" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
       <c r="B808">
         <v>2020</v>
       </c>
       <c r="C808" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D808" t="s">
         <v>1140</v>
-      </c>
-      <c r="D808" t="s">
-        <v>1141</v>
       </c>
     </row>
     <row r="809" spans="1:5" x14ac:dyDescent="0.2">
@@ -14843,10 +14878,10 @@
         <v>2020</v>
       </c>
       <c r="C809" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D809" t="s">
         <v>1142</v>
-      </c>
-      <c r="D809" t="s">
-        <v>1143</v>
       </c>
     </row>
     <row r="810" spans="1:5" x14ac:dyDescent="0.2">
@@ -14855,10 +14890,10 @@
         <v>2020</v>
       </c>
       <c r="C810" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="D810" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="811" spans="1:5" x14ac:dyDescent="0.2">
@@ -14867,7 +14902,7 @@
         <v>2020</v>
       </c>
       <c r="C811" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="D811" t="s">
         <v>739</v>
@@ -14879,10 +14914,10 @@
         <v>2020</v>
       </c>
       <c r="C812" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D812" t="s">
         <v>1146</v>
-      </c>
-      <c r="D812" t="s">
-        <v>1147</v>
       </c>
     </row>
     <row r="813" spans="1:5" x14ac:dyDescent="0.2">
@@ -14891,13 +14926,13 @@
         <v>2020</v>
       </c>
       <c r="C813" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="D813" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="E813" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="814" spans="1:5" x14ac:dyDescent="0.2">
@@ -14906,7 +14941,7 @@
         <v>2020</v>
       </c>
       <c r="C814" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="D814" t="s">
         <v>805</v>
@@ -14918,21 +14953,21 @@
         <v>2020</v>
       </c>
       <c r="C815" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="D815" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="816" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A816" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="B816">
         <v>2020</v>
       </c>
       <c r="C816" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="D816" t="s">
         <v>819</v>
@@ -14944,7 +14979,7 @@
         <v>2020</v>
       </c>
       <c r="C817" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="D817" t="s">
         <v>312</v>
@@ -14956,7 +14991,7 @@
         <v>2020</v>
       </c>
       <c r="C818" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="D818" t="s">
         <v>597</v>
@@ -14968,10 +15003,10 @@
         <v>2020</v>
       </c>
       <c r="C819" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D819" t="s">
         <v>1154</v>
-      </c>
-      <c r="D819" t="s">
-        <v>1155</v>
       </c>
     </row>
     <row r="820" spans="1:5" x14ac:dyDescent="0.2">
@@ -14980,10 +15015,10 @@
         <v>2020</v>
       </c>
       <c r="C820" t="s">
+        <v>1155</v>
+      </c>
+      <c r="D820" t="s">
         <v>1156</v>
-      </c>
-      <c r="D820" t="s">
-        <v>1157</v>
       </c>
     </row>
     <row r="821" spans="1:5" x14ac:dyDescent="0.2">
@@ -14992,10 +15027,10 @@
         <v>2020</v>
       </c>
       <c r="C821" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D821" t="s">
         <v>1158</v>
-      </c>
-      <c r="D821" t="s">
-        <v>1159</v>
       </c>
     </row>
     <row r="822" spans="1:5" x14ac:dyDescent="0.2">
@@ -15004,10 +15039,10 @@
         <v>2020</v>
       </c>
       <c r="C822" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D822" t="s">
         <v>1160</v>
-      </c>
-      <c r="D822" t="s">
-        <v>1161</v>
       </c>
     </row>
     <row r="823" spans="1:5" x14ac:dyDescent="0.2">
@@ -15016,7 +15051,7 @@
         <v>2020</v>
       </c>
       <c r="C823" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="D823" t="s">
         <v>531</v>
@@ -15028,13 +15063,13 @@
         <v>2020</v>
       </c>
       <c r="C824" t="s">
+        <v>1162</v>
+      </c>
+      <c r="D824" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E824" t="s">
         <v>1163</v>
-      </c>
-      <c r="D824" t="s">
-        <v>1128</v>
-      </c>
-      <c r="E824" t="s">
-        <v>1164</v>
       </c>
     </row>
     <row r="825" spans="1:5" x14ac:dyDescent="0.2">
@@ -15043,10 +15078,10 @@
         <v>2020</v>
       </c>
       <c r="C825" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="D825" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="826" spans="1:5" x14ac:dyDescent="0.2">
@@ -15055,7 +15090,7 @@
         <v>2020</v>
       </c>
       <c r="C826" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="D826" t="s">
         <v>166</v>
@@ -15067,7 +15102,7 @@
         <v>2020</v>
       </c>
       <c r="C827" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="D827" t="s">
         <v>360</v>
@@ -15082,7 +15117,7 @@
         <v>2020</v>
       </c>
       <c r="C828" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="D828" t="s">
         <v>19</v>
@@ -15094,10 +15129,10 @@
         <v>2020</v>
       </c>
       <c r="C829" t="s">
+        <v>1168</v>
+      </c>
+      <c r="D829" t="s">
         <v>1169</v>
-      </c>
-      <c r="D829" t="s">
-        <v>1170</v>
       </c>
     </row>
     <row r="830" spans="1:5" x14ac:dyDescent="0.2">
@@ -15106,7 +15141,7 @@
         <v>2020</v>
       </c>
       <c r="C830" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="D830" t="s">
         <v>698</v>
@@ -15118,10 +15153,10 @@
         <v>2020</v>
       </c>
       <c r="C831" t="s">
+        <v>1171</v>
+      </c>
+      <c r="D831" t="s">
         <v>1172</v>
-      </c>
-      <c r="D831" t="s">
-        <v>1173</v>
       </c>
     </row>
     <row r="832" spans="1:5" x14ac:dyDescent="0.2">
@@ -15130,7 +15165,7 @@
         <v>2020</v>
       </c>
       <c r="C832" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="D832" t="s">
         <v>782</v>
@@ -15138,13 +15173,13 @@
     </row>
     <row r="833" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A833" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B833">
         <v>2020</v>
       </c>
       <c r="C833" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="D833" t="s">
         <v>539</v>
@@ -15156,7 +15191,7 @@
         <v>2020</v>
       </c>
       <c r="C834" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="D834" t="s">
         <v>819</v>
@@ -15168,10 +15203,10 @@
         <v>2020</v>
       </c>
       <c r="C835" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="D835" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="836" spans="1:5" x14ac:dyDescent="0.2">
@@ -15180,24 +15215,24 @@
         <v>2020</v>
       </c>
       <c r="C836" t="s">
+        <v>1177</v>
+      </c>
+      <c r="D836" t="s">
         <v>1178</v>
-      </c>
-      <c r="D836" t="s">
-        <v>1179</v>
       </c>
     </row>
     <row r="837" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A837" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="B837">
         <v>2020</v>
       </c>
       <c r="C837" t="s">
+        <v>1179</v>
+      </c>
+      <c r="D837" t="s">
         <v>1180</v>
-      </c>
-      <c r="D837" t="s">
-        <v>1181</v>
       </c>
     </row>
     <row r="838" spans="1:5" x14ac:dyDescent="0.2">
@@ -15206,7 +15241,7 @@
         <v>2020</v>
       </c>
       <c r="C838" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="D838" t="s">
         <v>519</v>
@@ -15214,16 +15249,16 @@
     </row>
     <row r="839" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A839" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B839">
         <v>2020</v>
       </c>
       <c r="C839" t="s">
+        <v>1182</v>
+      </c>
+      <c r="D839" t="s">
         <v>1183</v>
-      </c>
-      <c r="D839" t="s">
-        <v>1184</v>
       </c>
     </row>
     <row r="840" spans="1:5" x14ac:dyDescent="0.2">
@@ -15232,10 +15267,10 @@
         <v>2020</v>
       </c>
       <c r="C840" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="D840" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="841" spans="1:5" x14ac:dyDescent="0.2">
@@ -15244,24 +15279,24 @@
         <v>2020</v>
       </c>
       <c r="C841" t="s">
+        <v>1185</v>
+      </c>
+      <c r="D841" t="s">
         <v>1186</v>
-      </c>
-      <c r="D841" t="s">
-        <v>1187</v>
       </c>
     </row>
     <row r="842" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A842" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="B842">
         <v>2020</v>
       </c>
       <c r="C842" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="D842" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="843" spans="1:5" x14ac:dyDescent="0.2">
@@ -15270,10 +15305,10 @@
         <v>2021</v>
       </c>
       <c r="C843" t="s">
+        <v>1188</v>
+      </c>
+      <c r="D843" t="s">
         <v>1189</v>
-      </c>
-      <c r="D843" t="s">
-        <v>1190</v>
       </c>
     </row>
     <row r="844" spans="1:5" x14ac:dyDescent="0.2">
@@ -15282,24 +15317,24 @@
         <v>2021</v>
       </c>
       <c r="C844" t="s">
+        <v>1190</v>
+      </c>
+      <c r="D844" t="s">
         <v>1191</v>
-      </c>
-      <c r="D844" t="s">
-        <v>1192</v>
       </c>
     </row>
     <row r="845" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A845" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="B845">
         <v>2021</v>
       </c>
       <c r="C845" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="D845" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="846" spans="1:5" x14ac:dyDescent="0.2">
@@ -15308,7 +15343,7 @@
         <v>2021</v>
       </c>
       <c r="C846" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="D846" t="s">
         <v>739</v>
@@ -15323,7 +15358,7 @@
         <v>2021</v>
       </c>
       <c r="C847" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="D847" t="s">
         <v>760</v>
@@ -15335,7 +15370,7 @@
         <v>2021</v>
       </c>
       <c r="C848" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="D848" t="s">
         <v>767</v>
@@ -15347,10 +15382,10 @@
         <v>2021</v>
       </c>
       <c r="C849" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D849" t="s">
         <v>1196</v>
-      </c>
-      <c r="D849" t="s">
-        <v>1197</v>
       </c>
     </row>
     <row r="850" spans="1:5" x14ac:dyDescent="0.2">
@@ -15359,10 +15394,10 @@
         <v>2021</v>
       </c>
       <c r="C850" t="s">
+        <v>1197</v>
+      </c>
+      <c r="D850" t="s">
         <v>1198</v>
-      </c>
-      <c r="D850" t="s">
-        <v>1199</v>
       </c>
     </row>
     <row r="851" spans="1:5" x14ac:dyDescent="0.2">
@@ -15371,7 +15406,7 @@
         <v>2021</v>
       </c>
       <c r="C851" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="D851" t="s">
         <v>366</v>
@@ -15383,7 +15418,7 @@
         <v>2021</v>
       </c>
       <c r="C852" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="D852" t="s">
         <v>418</v>
@@ -15391,36 +15426,36 @@
     </row>
     <row r="853" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A853" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="B853">
         <v>2021</v>
       </c>
       <c r="C853" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="D853" t="s">
+        <v>1201</v>
+      </c>
+      <c r="E853" t="s">
         <v>1202</v>
-      </c>
-      <c r="E853" t="s">
-        <v>1203</v>
       </c>
     </row>
     <row r="854" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A854" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B854">
         <v>2021</v>
       </c>
       <c r="C854" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="D854" t="s">
         <v>526</v>
       </c>
       <c r="E854" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="855" spans="1:5" x14ac:dyDescent="0.2">
@@ -15429,10 +15464,10 @@
         <v>2021</v>
       </c>
       <c r="C855" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="D855" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="856" spans="1:5" x14ac:dyDescent="0.2">
@@ -15441,7 +15476,7 @@
         <v>2021</v>
       </c>
       <c r="C856" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="D856" t="s">
         <v>601</v>
@@ -15453,7 +15488,7 @@
         <v>2021</v>
       </c>
       <c r="C857" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D857" t="s">
         <v>624</v>
@@ -15464,16 +15499,16 @@
     </row>
     <row r="858" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A858" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="B858">
         <v>2021</v>
       </c>
       <c r="C858" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D858" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="859" spans="1:5" x14ac:dyDescent="0.2">
@@ -15482,7 +15517,7 @@
         <v>2021</v>
       </c>
       <c r="C859" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="D859" t="s">
         <v>787</v>
@@ -15494,38 +15529,38 @@
         <v>2021</v>
       </c>
       <c r="C860" t="s">
+        <v>1210</v>
+      </c>
+      <c r="D860" t="s">
         <v>1211</v>
-      </c>
-      <c r="D860" t="s">
-        <v>1212</v>
       </c>
     </row>
     <row r="861" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A861" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="B861">
         <v>2021</v>
       </c>
       <c r="C861" t="s">
+        <v>1212</v>
+      </c>
+      <c r="D861" t="s">
         <v>1213</v>
-      </c>
-      <c r="D861" t="s">
-        <v>1214</v>
       </c>
     </row>
     <row r="862" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A862" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B862">
         <v>2022</v>
       </c>
       <c r="C862" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D862" t="s">
         <v>1215</v>
-      </c>
-      <c r="D862" t="s">
-        <v>1216</v>
       </c>
     </row>
     <row r="863" spans="1:5" x14ac:dyDescent="0.2">
@@ -15534,7 +15569,7 @@
         <v>2022</v>
       </c>
       <c r="C863" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="D863" t="s">
         <v>751</v>
@@ -15542,27 +15577,27 @@
     </row>
     <row r="864" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A864" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B864">
         <v>2022</v>
       </c>
       <c r="C864" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D864" t="s">
         <v>1218</v>
-      </c>
-      <c r="D864" t="s">
-        <v>1219</v>
       </c>
     </row>
     <row r="865" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A865" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B865">
         <v>2022</v>
       </c>
       <c r="C865" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="D865" t="s">
         <v>554</v>
@@ -15574,7 +15609,7 @@
         <v>2022</v>
       </c>
       <c r="C866" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="D866" t="s">
         <v>160</v>
@@ -15586,10 +15621,10 @@
         <v>2022</v>
       </c>
       <c r="C867" t="s">
+        <v>1221</v>
+      </c>
+      <c r="D867" t="s">
         <v>1222</v>
-      </c>
-      <c r="D867" t="s">
-        <v>1223</v>
       </c>
     </row>
     <row r="868" spans="1:5" x14ac:dyDescent="0.2">
@@ -15598,10 +15633,10 @@
         <v>2022</v>
       </c>
       <c r="C868" t="s">
+        <v>1223</v>
+      </c>
+      <c r="D868" t="s">
         <v>1224</v>
-      </c>
-      <c r="D868" t="s">
-        <v>1225</v>
       </c>
     </row>
     <row r="869" spans="1:5" x14ac:dyDescent="0.2">
@@ -15610,10 +15645,10 @@
         <v>2022</v>
       </c>
       <c r="C869" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="D869" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="870" spans="1:5" x14ac:dyDescent="0.2">
@@ -15622,7 +15657,7 @@
         <v>2022</v>
       </c>
       <c r="C870" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D870" t="s">
         <v>760</v>
@@ -15634,10 +15669,10 @@
         <v>2022</v>
       </c>
       <c r="C871" t="s">
+        <v>1227</v>
+      </c>
+      <c r="D871" t="s">
         <v>1228</v>
-      </c>
-      <c r="D871" t="s">
-        <v>1229</v>
       </c>
     </row>
     <row r="872" spans="1:5" x14ac:dyDescent="0.2">
@@ -15646,10 +15681,10 @@
         <v>2022</v>
       </c>
       <c r="C872" t="s">
+        <v>1229</v>
+      </c>
+      <c r="D872" t="s">
         <v>1230</v>
-      </c>
-      <c r="D872" t="s">
-        <v>1231</v>
       </c>
     </row>
     <row r="873" spans="1:5" x14ac:dyDescent="0.2">
@@ -15658,7 +15693,7 @@
         <v>2022</v>
       </c>
       <c r="C873" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="D873" t="s">
         <v>160</v>
@@ -15670,7 +15705,7 @@
         <v>2022</v>
       </c>
       <c r="C874" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="D874" t="s">
         <v>17</v>
@@ -15682,7 +15717,7 @@
         <v>2022</v>
       </c>
       <c r="C875" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="D875" t="s">
         <v>805</v>
@@ -15694,10 +15729,10 @@
         <v>2022</v>
       </c>
       <c r="C876" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="D876" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="877" spans="1:5" x14ac:dyDescent="0.2">
@@ -15706,13 +15741,13 @@
         <v>2022</v>
       </c>
       <c r="C877" t="s">
+        <v>1234</v>
+      </c>
+      <c r="D877" t="s">
         <v>1235</v>
       </c>
-      <c r="D877" t="s">
+      <c r="E877" t="s">
         <v>1236</v>
-      </c>
-      <c r="E877" t="s">
-        <v>1237</v>
       </c>
     </row>
     <row r="878" spans="1:5" x14ac:dyDescent="0.2">
@@ -15721,27 +15756,27 @@
         <v>2022</v>
       </c>
       <c r="C878" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="D878" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="879" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A879" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="B879">
         <v>2022</v>
       </c>
       <c r="C879" t="s">
+        <v>1238</v>
+      </c>
+      <c r="D879" t="s">
         <v>1239</v>
       </c>
-      <c r="D879" t="s">
+      <c r="E879" t="s">
         <v>1240</v>
-      </c>
-      <c r="E879" t="s">
-        <v>1241</v>
       </c>
     </row>
     <row r="880" spans="1:5" x14ac:dyDescent="0.2">
@@ -15750,7 +15785,7 @@
         <v>2022</v>
       </c>
       <c r="C880" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="D880" t="s">
         <v>160</v>
@@ -15762,7 +15797,7 @@
         <v>2022</v>
       </c>
       <c r="C881" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="D881" t="s">
         <v>659</v>
@@ -15770,16 +15805,16 @@
     </row>
     <row r="882" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A882" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B882">
         <v>2022</v>
       </c>
       <c r="C882" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="D882" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="883" spans="1:4" x14ac:dyDescent="0.2">
@@ -15788,7 +15823,7 @@
         <v>2022</v>
       </c>
       <c r="C883" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="D883" t="s">
         <v>642</v>
@@ -15800,7 +15835,7 @@
         <v>2022</v>
       </c>
       <c r="C884" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="D884" t="s">
         <v>390</v>
@@ -15812,7 +15847,7 @@
         <v>2022</v>
       </c>
       <c r="C885" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="D885" t="s">
         <v>588</v>
@@ -15820,16 +15855,16 @@
     </row>
     <row r="886" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A886" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B886">
         <v>2022</v>
       </c>
       <c r="C886" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D886" t="s">
         <v>1248</v>
-      </c>
-      <c r="D886" t="s">
-        <v>1249</v>
       </c>
     </row>
     <row r="887" spans="1:4" x14ac:dyDescent="0.2">
@@ -15838,7 +15873,7 @@
         <v>2022</v>
       </c>
       <c r="C887" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="D887" t="s">
         <v>531</v>
@@ -15850,7 +15885,7 @@
         <v>2022</v>
       </c>
       <c r="C888" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="D888" t="s">
         <v>324</v>
@@ -15862,10 +15897,10 @@
         <v>2023</v>
       </c>
       <c r="C889" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="D889" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="890" spans="1:4" x14ac:dyDescent="0.2">
@@ -15874,7 +15909,7 @@
         <v>2023</v>
       </c>
       <c r="C890" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="D890" t="s">
         <v>531</v>
@@ -15886,7 +15921,7 @@
         <v>2023</v>
       </c>
       <c r="C891" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="D891" t="s">
         <v>526</v>
@@ -15898,7 +15933,7 @@
         <v>2023</v>
       </c>
       <c r="C892" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="D892" t="s">
         <v>134</v>
@@ -15910,7 +15945,7 @@
         <v>2023</v>
       </c>
       <c r="C893" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="D893" t="s">
         <v>614</v>
@@ -15922,7 +15957,7 @@
         <v>2023</v>
       </c>
       <c r="C894" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="D894" t="s">
         <v>463</v>
@@ -15934,38 +15969,38 @@
         <v>2023</v>
       </c>
       <c r="C895" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="D895" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="896" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A896" t="s">
-        <v>1376</v>
-      </c>
-      <c r="B896">
+    <row r="896" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A896" s="3" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B896" s="3">
         <v>2023</v>
       </c>
-      <c r="C896" t="s">
+      <c r="C896" s="3" t="s">
+        <v>1258</v>
+      </c>
+      <c r="D896" s="3" t="s">
         <v>1259</v>
-      </c>
-      <c r="D896" t="s">
-        <v>1260</v>
       </c>
     </row>
     <row r="897" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A897" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B897">
         <v>2023</v>
       </c>
       <c r="C897" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="D897" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="898" spans="1:5" x14ac:dyDescent="0.2">
@@ -15974,7 +16009,7 @@
         <v>2023</v>
       </c>
       <c r="C898" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="D898" t="s">
         <v>526</v>
@@ -15986,7 +16021,7 @@
         <v>2023</v>
       </c>
       <c r="C899" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="D899" t="s">
         <v>531</v>
@@ -15994,55 +16029,55 @@
     </row>
     <row r="900" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A900" s="2" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="B900" s="2">
         <v>2024</v>
       </c>
       <c r="C900" s="2" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
       <c r="D900" s="2" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="901" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A901" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B901">
         <v>2025</v>
       </c>
       <c r="C901" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="D901" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="902" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A902" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="B902">
         <v>2025</v>
       </c>
       <c r="C902" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="D902" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="903" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A903" s="1" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="B903">
         <v>1976</v>
       </c>
       <c r="C903" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="D903" t="s">
         <v>92</v>
@@ -16050,13 +16085,13 @@
     </row>
     <row r="904" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A904" s="1" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B904">
         <v>1971</v>
       </c>
       <c r="C904" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="D904" t="s">
         <v>87</v>
@@ -16064,16 +16099,16 @@
     </row>
     <row r="905" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A905" s="1" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B905">
         <v>2024</v>
       </c>
       <c r="C905" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="D905" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="906" spans="1:5" x14ac:dyDescent="0.2">
@@ -16081,21 +16116,21 @@
         <v>2025</v>
       </c>
       <c r="C906" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="D906" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="907" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A907" s="1" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B907">
         <v>1970</v>
       </c>
       <c r="C907" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="D907" t="s">
         <v>134</v>
@@ -16103,27 +16138,27 @@
     </row>
     <row r="908" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A908" s="1" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B908">
         <v>1973</v>
       </c>
       <c r="C908" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="D908" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="909" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A909" s="1" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B909">
         <v>1971</v>
       </c>
       <c r="C909" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="D909" t="s">
         <v>681</v>
@@ -16131,13 +16166,13 @@
     </row>
     <row r="910" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A910" s="1" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="B910">
         <v>2006</v>
       </c>
       <c r="C910" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
       <c r="D910" t="s">
         <v>280</v>
@@ -16145,13 +16180,13 @@
     </row>
     <row r="911" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A911" s="1" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="B911">
         <v>1947</v>
       </c>
       <c r="C911" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
       <c r="D911" t="s">
         <v>81</v>
@@ -16159,173 +16194,246 @@
     </row>
     <row r="912" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A912" s="1" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="B912">
         <v>1956</v>
       </c>
       <c r="C912" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
       <c r="D912" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
       <c r="E912" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="913" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="913" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A913" s="1" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="B913">
         <v>1958</v>
       </c>
       <c r="C913" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="D913" t="s">
-        <v>1352</v>
-      </c>
-    </row>
-    <row r="914" spans="1:4" x14ac:dyDescent="0.2">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="914" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A914" s="1" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B914">
         <v>1974</v>
       </c>
       <c r="C914" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="D914" t="s">
-        <v>1354</v>
-      </c>
-    </row>
-    <row r="915" spans="1:4" x14ac:dyDescent="0.2">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="915" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A915" s="1" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B915">
         <v>1986</v>
       </c>
       <c r="C915" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="D915" t="s">
-        <v>1356</v>
-      </c>
-    </row>
-    <row r="916" spans="1:4" x14ac:dyDescent="0.2">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="916" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A916" s="1" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B916">
         <v>1976</v>
       </c>
       <c r="C916" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="D916" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="917" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="917" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A917" s="1" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="B917">
         <v>2005</v>
       </c>
       <c r="C917" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="D917" t="s">
-        <v>1360</v>
-      </c>
-    </row>
-    <row r="918" spans="1:4" x14ac:dyDescent="0.2">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="918" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A918" s="1" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B918">
         <v>1999</v>
       </c>
       <c r="C918" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="D918" t="s">
-        <v>1362</v>
-      </c>
-    </row>
-    <row r="919" spans="1:4" x14ac:dyDescent="0.2">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="919" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A919" s="1" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="B919">
         <v>1959</v>
       </c>
       <c r="C919" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="D919" t="s">
-        <v>1365</v>
-      </c>
-    </row>
-    <row r="920" spans="1:4" x14ac:dyDescent="0.2">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="920" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A920" s="1" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="B920">
         <v>2024</v>
       </c>
       <c r="C920" t="s">
+        <v>1364</v>
+      </c>
+      <c r="D920" t="s">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="921" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A921" s="1" t="s">
         <v>1366</v>
-      </c>
-      <c r="D920" t="s">
-        <v>1367</v>
-      </c>
-    </row>
-    <row r="921" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A921" s="1" t="s">
-        <v>1368</v>
       </c>
       <c r="B921">
         <v>1963</v>
       </c>
       <c r="C921" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="D921" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="922" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="922" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A922" s="1" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B922">
         <v>2010</v>
       </c>
       <c r="C922" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="D922" t="s">
-        <v>1386</v>
-      </c>
-    </row>
-    <row r="923" spans="1:4" x14ac:dyDescent="0.2">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="923" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A923" s="1" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="B923">
         <v>2005</v>
       </c>
       <c r="C923" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="D923" t="s">
-        <v>1388</v>
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="924" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A924" s="4" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B924" s="3">
+        <v>1966</v>
+      </c>
+      <c r="C924" s="3" t="s">
+        <v>1390</v>
+      </c>
+      <c r="D924" s="3" t="s">
+        <v>1389</v>
+      </c>
+    </row>
+    <row r="925" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A925" s="1" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B925">
+        <v>1966</v>
+      </c>
+      <c r="C925" t="s">
+        <v>1391</v>
+      </c>
+      <c r="D925" t="s">
+        <v>1392</v>
+      </c>
+      <c r="E925" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="926" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A926" s="1" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B926">
+        <v>1972</v>
+      </c>
+      <c r="C926" t="s">
+        <v>1393</v>
+      </c>
+      <c r="D926" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="927" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A927" s="1" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B927">
+        <v>1968</v>
+      </c>
+      <c r="C927" t="s">
+        <v>1394</v>
+      </c>
+      <c r="D927" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="928" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A928" s="1" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B928">
+        <v>1983</v>
+      </c>
+      <c r="C928" t="s">
+        <v>1396</v>
+      </c>
+      <c r="D928" t="s">
+        <v>1397</v>
       </c>
     </row>
   </sheetData>
@@ -16340,39 +16448,39 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="B1" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B2" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B3" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="B4" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B5" t="s">
         <v>399</v>
@@ -16380,82 +16488,82 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="B6" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="B7" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="B8" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="B9" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
       <c r="B10" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="B11" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="23" spans="7:11" x14ac:dyDescent="0.2">
       <c r="G23" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="24" spans="7:11" x14ac:dyDescent="0.2">
       <c r="G24" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="25" spans="7:11" x14ac:dyDescent="0.2">
       <c r="G25" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="26" spans="7:11" x14ac:dyDescent="0.2">
       <c r="G26" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
       <c r="H26" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="I26" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="J26" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="K26" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
     </row>
   </sheetData>
